--- a/resources/variable_schema_data_individual_roster_template.xlsx
+++ b/resources/variable_schema_data_individual_roster_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE630A4-AC78-4908-8DCA-CE6E90EB78EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB383FE-3EB9-4BD4-86D8-E15F5243DD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14280" yWindow="0" windowWidth="14625" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="319">
   <si>
     <t>rule_type</t>
   </si>
@@ -761,6 +761,222 @@
   </si>
   <si>
     <t>عدد أيام العمل للإناث (بالأيام)</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>enum_id,enumerator_id,enumerator,enum,surveyor_id</t>
+  </si>
+  <si>
+    <t>Enumerator ID</t>
+  </si>
+  <si>
+    <t>ID de l'enquêteur</t>
+  </si>
+  <si>
+    <t>معرف المعداد</t>
+  </si>
+  <si>
+    <t>device_id</t>
+  </si>
+  <si>
+    <t>device_id,deviceid,device,device_identifier</t>
+  </si>
+  <si>
+    <t>Device ID</t>
+  </si>
+  <si>
+    <t>ID de l'appareil</t>
+  </si>
+  <si>
+    <t>معرف الجهاز</t>
+  </si>
+  <si>
+    <t>gps_lat</t>
+  </si>
+  <si>
+    <t>gps</t>
+  </si>
+  <si>
+    <t>gps_lat,latitude,lat,_gps_latitude,gps_latitude</t>
+  </si>
+  <si>
+    <t>GPS Latitude</t>
+  </si>
+  <si>
+    <t>Latitude GPS</t>
+  </si>
+  <si>
+    <t>خط العرض GPS</t>
+  </si>
+  <si>
+    <t>gps_lon</t>
+  </si>
+  <si>
+    <t>gps_lon,longitude,lon,lng,_gps_longitude,gps_longitude</t>
+  </si>
+  <si>
+    <t>GPS Longitude</t>
+  </si>
+  <si>
+    <t>Longitude GPS</t>
+  </si>
+  <si>
+    <t>خط الطول GPS</t>
+  </si>
+  <si>
+    <t>gps_precision</t>
+  </si>
+  <si>
+    <t>gps_precision,gps_accuracy,accuracy</t>
+  </si>
+  <si>
+    <t>GPS Precision</t>
+  </si>
+  <si>
+    <t>Précision GPS</t>
+  </si>
+  <si>
+    <t>دقة GPS</t>
+  </si>
+  <si>
+    <t>GPS precision</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>weight,sampling_weight,survey_weight,wt</t>
+  </si>
+  <si>
+    <t>Sampling Weight</t>
+  </si>
+  <si>
+    <t>Poids d'échantillonnage</t>
+  </si>
+  <si>
+    <t>وزن العينة</t>
+  </si>
+  <si>
+    <t>Sampling weight</t>
+  </si>
+  <si>
+    <t>stratum</t>
+  </si>
+  <si>
+    <t>stratum,strata,survey_stratum</t>
+  </si>
+  <si>
+    <t>Stratum</t>
+  </si>
+  <si>
+    <t>Strate</t>
+  </si>
+  <si>
+    <t>الطبقة</t>
+  </si>
+  <si>
+    <t>Survey stratum</t>
+  </si>
+  <si>
+    <t>cluster_id</t>
+  </si>
+  <si>
+    <t>cluster_id,cluster,psu,primary_sampling_unit</t>
+  </si>
+  <si>
+    <t>Cluster ID</t>
+  </si>
+  <si>
+    <t>ID de la grappe</t>
+  </si>
+  <si>
+    <t>معرف العنقود</t>
+  </si>
+  <si>
+    <t>Primary sampling unit</t>
+  </si>
+  <si>
+    <t>cluster_id_numeric</t>
+  </si>
+  <si>
+    <t>site</t>
+  </si>
+  <si>
+    <t>site,location,assessment_site,site_name</t>
+  </si>
+  <si>
+    <t>Survey Site</t>
+  </si>
+  <si>
+    <t>Site d'enquête</t>
+  </si>
+  <si>
+    <t>موقع الاستبيان</t>
+  </si>
+  <si>
+    <t>Assessment site</t>
+  </si>
+  <si>
+    <t>admin1</t>
+  </si>
+  <si>
+    <t>admin1,adm1,region,state,province,governorate</t>
+  </si>
+  <si>
+    <t>Administrative Area 1</t>
+  </si>
+  <si>
+    <t>Zone administrative 1</t>
+  </si>
+  <si>
+    <t>المنطقة الإدارية 1</t>
+  </si>
+  <si>
+    <t>admin2</t>
+  </si>
+  <si>
+    <t>admin2,adm2,district,county,zone</t>
+  </si>
+  <si>
+    <t>Administrative Area 2</t>
+  </si>
+  <si>
+    <t>Zone administrative 2</t>
+  </si>
+  <si>
+    <t>المنطقة الإدارية 2</t>
+  </si>
+  <si>
+    <t>admin3</t>
+  </si>
+  <si>
+    <t>admin3,adm3,sub_district,commune,ward</t>
+  </si>
+  <si>
+    <t>Administrative Area 3</t>
+  </si>
+  <si>
+    <t>Zone administrative 3</t>
+  </si>
+  <si>
+    <t>المنطقة الإدارية 3</t>
+  </si>
+  <si>
+    <t>admin4</t>
+  </si>
+  <si>
+    <t>admin4,adm4,village,locality</t>
+  </si>
+  <si>
+    <t>Administrative Area 4</t>
+  </si>
+  <si>
+    <t>Zone administrative 4</t>
+  </si>
+  <si>
+    <t>المنطقة الإدارية 4</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S64"/>
+  <dimension ref="A1:S78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1267,25 +1483,28 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>247</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>248</v>
       </c>
       <c r="L4" t="s">
-        <v>34</v>
+        <v>249</v>
       </c>
       <c r="M4" t="s">
-        <v>35</v>
+        <v>250</v>
       </c>
       <c r="N4" t="s">
-        <v>36</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -1293,25 +1512,28 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>252</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>38</v>
+        <v>253</v>
       </c>
       <c r="L5" t="s">
-        <v>39</v>
+        <v>254</v>
       </c>
       <c r="M5" t="s">
-        <v>40</v>
+        <v>255</v>
       </c>
       <c r="N5" t="s">
-        <v>41</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -1319,25 +1541,25 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="M6" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -1345,40 +1567,25 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="L7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="M7" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="N7" t="s">
-        <v>55</v>
-      </c>
-      <c r="O7" t="s">
-        <v>56</v>
-      </c>
-      <c r="P7" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -1386,40 +1593,25 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="J8" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="L8" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N8" t="s">
-        <v>55</v>
-      </c>
-      <c r="O8" t="s">
-        <v>61</v>
-      </c>
-      <c r="P8" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -1427,25 +1619,40 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>50</v>
+      </c>
+      <c r="I9" t="s">
+        <v>51</v>
       </c>
       <c r="J9" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="L9" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="M9" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="N9" t="s">
-        <v>69</v>
+        <v>55</v>
+      </c>
+      <c r="O9" t="s">
+        <v>56</v>
+      </c>
+      <c r="P9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1453,10 +1660,10 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -1465,28 +1672,28 @@
         <v>50</v>
       </c>
       <c r="I10" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="L10" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="M10" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="N10" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="O10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="Q10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -1494,40 +1701,25 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="J11" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="N11" t="s">
-        <v>75</v>
-      </c>
-      <c r="O11" t="s">
-        <v>61</v>
-      </c>
-      <c r="P11" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -1535,25 +1727,31 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>257</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
       </c>
       <c r="E12" t="s">
         <v>43</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>258</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="L12" t="s">
-        <v>79</v>
+        <v>260</v>
       </c>
       <c r="M12" t="s">
-        <v>80</v>
+        <v>261</v>
       </c>
       <c r="N12" t="s">
-        <v>81</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -1561,25 +1759,31 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>263</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
       </c>
       <c r="E13" t="s">
         <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>258</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>83</v>
+        <v>264</v>
       </c>
       <c r="L13" t="s">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="M13" t="s">
-        <v>85</v>
+        <v>266</v>
       </c>
       <c r="N13" t="s">
-        <v>86</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -1587,25 +1791,34 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>268</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
       </c>
       <c r="E14" t="s">
         <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>258</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>88</v>
+        <v>269</v>
       </c>
       <c r="L14" t="s">
-        <v>89</v>
+        <v>270</v>
       </c>
       <c r="M14" t="s">
-        <v>90</v>
+        <v>271</v>
       </c>
       <c r="N14" t="s">
-        <v>91</v>
+        <v>272</v>
+      </c>
+      <c r="R14" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -1613,40 +1826,34 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" t="s">
-        <v>93</v>
+        <v>274</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" t="s">
-        <v>94</v>
+        <v>44</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>95</v>
+        <v>275</v>
       </c>
       <c r="L15" t="s">
-        <v>96</v>
+        <v>276</v>
       </c>
       <c r="M15" t="s">
-        <v>97</v>
+        <v>277</v>
       </c>
       <c r="N15" t="s">
-        <v>98</v>
-      </c>
-      <c r="O15" t="s">
-        <v>99</v>
-      </c>
-      <c r="P15" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>101</v>
+        <v>278</v>
+      </c>
+      <c r="R15" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -1654,293 +1861,254 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" t="s">
-        <v>102</v>
+        <v>280</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
       </c>
       <c r="E16" t="s">
         <v>20</v>
       </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" t="s">
-        <v>103</v>
+      <c r="G16" t="b">
+        <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="L16" t="s">
-        <v>96</v>
+        <v>282</v>
       </c>
       <c r="M16" t="s">
-        <v>97</v>
+        <v>283</v>
       </c>
       <c r="N16" t="s">
-        <v>98</v>
-      </c>
-      <c r="O16" t="s">
-        <v>104</v>
-      </c>
-      <c r="P16" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+      <c r="R16" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>286</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>108</v>
+        <v>287</v>
       </c>
       <c r="L17" t="s">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="M17" t="s">
-        <v>110</v>
+        <v>289</v>
       </c>
       <c r="N17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+      <c r="R17" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>292</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" t="s">
-        <v>32</v>
+        <v>43</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>113</v>
+        <v>292</v>
       </c>
       <c r="L18" t="s">
-        <v>114</v>
+        <v>288</v>
       </c>
       <c r="M18" t="s">
-        <v>115</v>
+        <v>289</v>
       </c>
       <c r="N18" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+      <c r="R18" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>293</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>118</v>
+        <v>294</v>
       </c>
       <c r="L19" t="s">
-        <v>119</v>
+        <v>295</v>
       </c>
       <c r="M19" t="s">
-        <v>120</v>
+        <v>296</v>
       </c>
       <c r="N19" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+      <c r="R19" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
-      </c>
-      <c r="C20" t="s">
-        <v>93</v>
+        <v>299</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
       </c>
       <c r="E20" t="s">
         <v>20</v>
       </c>
-      <c r="F20" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" t="s">
-        <v>94</v>
+      <c r="G20" t="b">
+        <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>123</v>
+        <v>300</v>
       </c>
       <c r="L20" t="s">
-        <v>124</v>
+        <v>301</v>
       </c>
       <c r="M20" t="s">
-        <v>125</v>
+        <v>302</v>
       </c>
       <c r="N20" t="s">
-        <v>126</v>
-      </c>
-      <c r="O20" t="s">
-        <v>99</v>
-      </c>
-      <c r="P20" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" t="s">
-        <v>102</v>
+        <v>304</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
       </c>
       <c r="E21" t="s">
         <v>20</v>
       </c>
-      <c r="F21" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" t="s">
-        <v>103</v>
+      <c r="G21" t="b">
+        <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>123</v>
+        <v>305</v>
       </c>
       <c r="L21" t="s">
-        <v>124</v>
+        <v>306</v>
       </c>
       <c r="M21" t="s">
-        <v>125</v>
+        <v>307</v>
       </c>
       <c r="N21" t="s">
-        <v>126</v>
-      </c>
-      <c r="O21" t="s">
-        <v>104</v>
-      </c>
-      <c r="P21" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" t="s">
-        <v>128</v>
+        <v>309</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
       </c>
       <c r="E22" t="s">
         <v>20</v>
       </c>
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-      <c r="I22" t="s">
-        <v>129</v>
+      <c r="G22" t="b">
+        <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>130</v>
+        <v>310</v>
       </c>
       <c r="L22" t="s">
-        <v>131</v>
+        <v>311</v>
       </c>
       <c r="M22" t="s">
-        <v>132</v>
+        <v>312</v>
       </c>
       <c r="N22" t="s">
-        <v>133</v>
-      </c>
-      <c r="O22" t="s">
-        <v>134</v>
-      </c>
-      <c r="P22" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
-      </c>
-      <c r="C23" t="s">
-        <v>137</v>
+        <v>314</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
       </c>
       <c r="E23" t="s">
         <v>20</v>
       </c>
-      <c r="F23" t="s">
-        <v>50</v>
-      </c>
-      <c r="I23" t="s">
-        <v>138</v>
+      <c r="G23" t="b">
+        <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>130</v>
+        <v>315</v>
       </c>
       <c r="L23" t="s">
-        <v>131</v>
+        <v>316</v>
       </c>
       <c r="M23" t="s">
-        <v>132</v>
+        <v>317</v>
       </c>
       <c r="N23" t="s">
-        <v>133</v>
-      </c>
-      <c r="O23" t="s">
-        <v>139</v>
-      </c>
-      <c r="P23" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>142</v>
+        <v>49</v>
       </c>
       <c r="E24" t="s">
         <v>20</v>
@@ -1949,39 +2117,39 @@
         <v>50</v>
       </c>
       <c r="I24" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="J24" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="L24" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="M24" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="N24" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="O24" t="s">
-        <v>144</v>
+        <v>56</v>
       </c>
       <c r="P24" t="s">
-        <v>145</v>
+        <v>57</v>
       </c>
       <c r="Q24" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
         <v>20</v>
@@ -1990,315 +2158,240 @@
         <v>50</v>
       </c>
       <c r="I25" t="s">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="J25" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="L25" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="M25" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="N25" t="s">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="O25" t="s">
-        <v>149</v>
+        <v>61</v>
       </c>
       <c r="P25" t="s">
-        <v>150</v>
+        <v>62</v>
       </c>
       <c r="Q25" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>152</v>
-      </c>
-      <c r="C26" t="s">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="E26" t="s">
-        <v>154</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>44</v>
-      </c>
-      <c r="I26" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="J26" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="L26" t="s">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="M26" t="s">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="N26" t="s">
-        <v>158</v>
-      </c>
-      <c r="O26" t="s">
-        <v>153</v>
-      </c>
-      <c r="P26" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>152</v>
-      </c>
-      <c r="C27" t="s">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="E27" t="s">
-        <v>154</v>
+        <v>43</v>
       </c>
       <c r="F27" t="s">
         <v>44</v>
       </c>
-      <c r="I27" t="s">
-        <v>160</v>
-      </c>
       <c r="J27" t="s">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="L27" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="M27" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="N27" t="s">
-        <v>158</v>
-      </c>
-      <c r="O27" t="s">
-        <v>159</v>
-      </c>
-      <c r="P27" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
-      </c>
-      <c r="C28" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
-        <v>154</v>
+        <v>43</v>
       </c>
       <c r="F28" t="s">
         <v>44</v>
       </c>
-      <c r="I28" t="s">
-        <v>162</v>
-      </c>
       <c r="J28" t="s">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="L28" t="s">
-        <v>156</v>
+        <v>89</v>
       </c>
       <c r="M28" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="N28" t="s">
-        <v>158</v>
-      </c>
-      <c r="O28" t="s">
-        <v>161</v>
-      </c>
-      <c r="P28" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="F29" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I29" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="J29" t="s">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="L29" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="M29" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="N29" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="O29" t="s">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="P29" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="Q29" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="F30" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I30" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="J30" t="s">
-        <v>152</v>
+        <v>95</v>
       </c>
       <c r="L30" t="s">
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="M30" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="N30" t="s">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="O30" t="s">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="P30" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="Q30" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>152</v>
-      </c>
-      <c r="C31" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s">
-        <v>44</v>
-      </c>
-      <c r="I31" t="s">
-        <v>168</v>
+        <v>32</v>
       </c>
       <c r="J31" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="L31" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="M31" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="N31" t="s">
-        <v>158</v>
-      </c>
-      <c r="O31" t="s">
-        <v>167</v>
-      </c>
-      <c r="P31" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>152</v>
-      </c>
-      <c r="C32" t="s">
-        <v>169</v>
+        <v>112</v>
       </c>
       <c r="E32" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="F32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I32" t="s">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="J32" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="L32" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="M32" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="N32" t="s">
-        <v>158</v>
-      </c>
-      <c r="O32" t="s">
-        <v>169</v>
-      </c>
-      <c r="P32" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -2306,40 +2399,25 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
-      </c>
-      <c r="C33" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="E33" t="s">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="F33" t="s">
-        <v>44</v>
-      </c>
-      <c r="I33" t="s">
-        <v>172</v>
+        <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="L33" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="M33" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="N33" t="s">
-        <v>158</v>
-      </c>
-      <c r="O33" t="s">
-        <v>171</v>
-      </c>
-      <c r="P33" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -2347,40 +2425,40 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>173</v>
+        <v>93</v>
       </c>
       <c r="E34" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="F34" t="s">
         <v>44</v>
       </c>
       <c r="I34" t="s">
-        <v>174</v>
+        <v>94</v>
       </c>
       <c r="J34" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="L34" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="M34" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="N34" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="O34" t="s">
-        <v>173</v>
+        <v>99</v>
       </c>
       <c r="P34" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="Q34" t="s">
-        <v>173</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -2388,40 +2466,40 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="E35" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="F35" t="s">
         <v>44</v>
       </c>
       <c r="I35" t="s">
-        <v>176</v>
+        <v>103</v>
       </c>
       <c r="J35" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="L35" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="M35" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="N35" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="O35" t="s">
-        <v>175</v>
+        <v>104</v>
       </c>
       <c r="P35" t="s">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="Q35" t="s">
-        <v>175</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -2429,40 +2507,40 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="C36" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="E36" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="F36" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I36" t="s">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="J36" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="L36" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="M36" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="N36" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="O36" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="P36" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="Q36" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -2470,40 +2548,40 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I37" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="J37" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="L37" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="M37" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="N37" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="O37" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="P37" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="Q37" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -2511,40 +2589,40 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="C38" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="E38" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="F38" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I38" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="J38" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="L38" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="M38" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="N38" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="O38" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="P38" t="s">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="Q38" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -2552,40 +2630,40 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="E39" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="F39" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I39" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="J39" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="L39" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="M39" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="N39" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="O39" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="P39" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="Q39" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -2596,7 +2674,7 @@
         <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="E40" t="s">
         <v>154</v>
@@ -2605,7 +2683,7 @@
         <v>44</v>
       </c>
       <c r="I40" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="J40" t="s">
         <v>152</v>
@@ -2620,13 +2698,13 @@
         <v>158</v>
       </c>
       <c r="O40" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="P40" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="Q40" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -2637,7 +2715,7 @@
         <v>152</v>
       </c>
       <c r="C41" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="E41" t="s">
         <v>154</v>
@@ -2646,7 +2724,7 @@
         <v>44</v>
       </c>
       <c r="I41" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="J41" t="s">
         <v>152</v>
@@ -2661,13 +2739,13 @@
         <v>158</v>
       </c>
       <c r="O41" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="P41" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="Q41" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -2678,7 +2756,7 @@
         <v>152</v>
       </c>
       <c r="C42" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="E42" t="s">
         <v>154</v>
@@ -2687,7 +2765,7 @@
         <v>44</v>
       </c>
       <c r="I42" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="J42" t="s">
         <v>152</v>
@@ -2702,13 +2780,13 @@
         <v>158</v>
       </c>
       <c r="O42" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="P42" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="Q42" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -2719,7 +2797,7 @@
         <v>152</v>
       </c>
       <c r="C43" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="E43" t="s">
         <v>154</v>
@@ -2728,7 +2806,7 @@
         <v>44</v>
       </c>
       <c r="I43" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="J43" t="s">
         <v>152</v>
@@ -2743,13 +2821,13 @@
         <v>158</v>
       </c>
       <c r="O43" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="P43" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="Q43" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -2760,7 +2838,7 @@
         <v>152</v>
       </c>
       <c r="C44" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="E44" t="s">
         <v>154</v>
@@ -2769,7 +2847,7 @@
         <v>44</v>
       </c>
       <c r="I44" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="J44" t="s">
         <v>152</v>
@@ -2784,13 +2862,13 @@
         <v>158</v>
       </c>
       <c r="O44" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="P44" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="Q44" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -2801,7 +2879,7 @@
         <v>152</v>
       </c>
       <c r="C45" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="E45" t="s">
         <v>154</v>
@@ -2810,7 +2888,7 @@
         <v>44</v>
       </c>
       <c r="I45" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="J45" t="s">
         <v>152</v>
@@ -2825,13 +2903,13 @@
         <v>158</v>
       </c>
       <c r="O45" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="P45" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="Q45" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -2842,7 +2920,7 @@
         <v>152</v>
       </c>
       <c r="C46" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="E46" t="s">
         <v>154</v>
@@ -2851,7 +2929,7 @@
         <v>44</v>
       </c>
       <c r="I46" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="J46" t="s">
         <v>152</v>
@@ -2866,13 +2944,13 @@
         <v>158</v>
       </c>
       <c r="O46" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="P46" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="Q46" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -2883,7 +2961,7 @@
         <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="E47" t="s">
         <v>154</v>
@@ -2892,7 +2970,7 @@
         <v>44</v>
       </c>
       <c r="I47" t="s">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="J47" t="s">
         <v>152</v>
@@ -2907,13 +2985,13 @@
         <v>158</v>
       </c>
       <c r="O47" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="P47" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="Q47" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -2924,7 +3002,7 @@
         <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="E48" t="s">
         <v>154</v>
@@ -2933,7 +3011,7 @@
         <v>44</v>
       </c>
       <c r="I48" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="J48" t="s">
         <v>152</v>
@@ -2948,13 +3026,13 @@
         <v>158</v>
       </c>
       <c r="O48" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="P48" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="Q48" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -2965,7 +3043,7 @@
         <v>152</v>
       </c>
       <c r="C49" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="E49" t="s">
         <v>154</v>
@@ -2974,7 +3052,7 @@
         <v>44</v>
       </c>
       <c r="I49" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="J49" t="s">
         <v>152</v>
@@ -2989,13 +3067,13 @@
         <v>158</v>
       </c>
       <c r="O49" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="P49" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="Q49" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -3006,7 +3084,7 @@
         <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="E50" t="s">
         <v>154</v>
@@ -3015,7 +3093,7 @@
         <v>44</v>
       </c>
       <c r="I50" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="J50" t="s">
         <v>152</v>
@@ -3030,13 +3108,13 @@
         <v>158</v>
       </c>
       <c r="O50" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="P50" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="Q50" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -3044,10 +3122,10 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="C51" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="E51" t="s">
         <v>154</v>
@@ -3056,28 +3134,28 @@
         <v>44</v>
       </c>
       <c r="I51" t="s">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="J51" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="L51" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="M51" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="N51" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="O51" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="P51" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="Q51" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -3085,10 +3163,10 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="C52" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="E52" t="s">
         <v>154</v>
@@ -3097,28 +3175,28 @@
         <v>44</v>
       </c>
       <c r="I52" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="J52" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="L52" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="M52" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="N52" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="O52" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="P52" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="Q52" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -3126,10 +3204,10 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="E53" t="s">
         <v>154</v>
@@ -3138,28 +3216,28 @@
         <v>44</v>
       </c>
       <c r="I53" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="J53" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="L53" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="M53" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="N53" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="O53" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="P53" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="Q53" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -3167,10 +3245,10 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="C54" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="E54" t="s">
         <v>154</v>
@@ -3179,28 +3257,28 @@
         <v>44</v>
       </c>
       <c r="I54" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="J54" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="L54" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="M54" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="N54" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="O54" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="P54" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="Q54" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -3208,10 +3286,10 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="E55" t="s">
         <v>154</v>
@@ -3220,28 +3298,28 @@
         <v>44</v>
       </c>
       <c r="I55" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="J55" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="L55" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="M55" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="N55" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="O55" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="P55" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="Q55" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -3249,10 +3327,10 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="C56" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="E56" t="s">
         <v>154</v>
@@ -3261,28 +3339,28 @@
         <v>44</v>
       </c>
       <c r="I56" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="J56" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="L56" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="M56" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="N56" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="O56" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="P56" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="Q56" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -3290,10 +3368,10 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="C57" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="E57" t="s">
         <v>154</v>
@@ -3302,28 +3380,28 @@
         <v>44</v>
       </c>
       <c r="I57" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="J57" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="L57" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="M57" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="N57" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="O57" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="P57" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="Q57" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -3331,10 +3409,10 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="C58" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="E58" t="s">
         <v>154</v>
@@ -3343,28 +3421,28 @@
         <v>44</v>
       </c>
       <c r="I58" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="J58" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="L58" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="M58" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="N58" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="O58" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="P58" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="Q58" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -3372,10 +3450,10 @@
         <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="E59" t="s">
         <v>154</v>
@@ -3384,28 +3462,28 @@
         <v>44</v>
       </c>
       <c r="I59" t="s">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="J59" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="L59" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="M59" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="N59" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="O59" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="P59" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="Q59" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -3413,10 +3491,10 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="C60" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="E60" t="s">
         <v>154</v>
@@ -3425,28 +3503,28 @@
         <v>44</v>
       </c>
       <c r="I60" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="J60" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="L60" t="s">
-        <v>210</v>
+        <v>156</v>
       </c>
       <c r="M60" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="N60" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="O60" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="P60" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="Q60" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -3454,25 +3532,40 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>231</v>
+        <v>152</v>
+      </c>
+      <c r="C61" t="s">
+        <v>199</v>
       </c>
       <c r="E61" t="s">
-        <v>43</v>
+        <v>154</v>
       </c>
       <c r="F61" t="s">
         <v>44</v>
       </c>
+      <c r="I61" t="s">
+        <v>200</v>
+      </c>
       <c r="J61" t="s">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="L61" t="s">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="M61" t="s">
-        <v>239</v>
+        <v>157</v>
       </c>
       <c r="N61" t="s">
-        <v>243</v>
+        <v>158</v>
+      </c>
+      <c r="O61" t="s">
+        <v>199</v>
+      </c>
+      <c r="P61" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -3480,25 +3573,40 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>232</v>
+        <v>152</v>
+      </c>
+      <c r="C62" t="s">
+        <v>201</v>
       </c>
       <c r="E62" t="s">
-        <v>43</v>
+        <v>154</v>
       </c>
       <c r="F62" t="s">
         <v>44</v>
       </c>
+      <c r="I62" t="s">
+        <v>202</v>
+      </c>
       <c r="J62" t="s">
-        <v>232</v>
+        <v>152</v>
       </c>
       <c r="L62" t="s">
-        <v>238</v>
+        <v>156</v>
       </c>
       <c r="M62" t="s">
-        <v>240</v>
+        <v>157</v>
       </c>
       <c r="N62" t="s">
-        <v>244</v>
+        <v>158</v>
+      </c>
+      <c r="O62" t="s">
+        <v>201</v>
+      </c>
+      <c r="P62" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -3506,25 +3614,40 @@
         <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>233</v>
+        <v>152</v>
+      </c>
+      <c r="C63" t="s">
+        <v>203</v>
       </c>
       <c r="E63" t="s">
-        <v>43</v>
+        <v>154</v>
       </c>
       <c r="F63" t="s">
         <v>44</v>
       </c>
+      <c r="I63" t="s">
+        <v>204</v>
+      </c>
       <c r="J63" t="s">
-        <v>233</v>
+        <v>152</v>
       </c>
       <c r="L63" t="s">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="M63" t="s">
-        <v>241</v>
+        <v>157</v>
       </c>
       <c r="N63" t="s">
-        <v>245</v>
+        <v>158</v>
+      </c>
+      <c r="O63" t="s">
+        <v>203</v>
+      </c>
+      <c r="P63" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -3532,35 +3655,564 @@
         <v>1</v>
       </c>
       <c r="B64" t="s">
+        <v>152</v>
+      </c>
+      <c r="C64" t="s">
+        <v>205</v>
+      </c>
+      <c r="E64" t="s">
+        <v>154</v>
+      </c>
+      <c r="F64" t="s">
+        <v>44</v>
+      </c>
+      <c r="I64" t="s">
+        <v>206</v>
+      </c>
+      <c r="J64" t="s">
+        <v>152</v>
+      </c>
+      <c r="L64" t="s">
+        <v>156</v>
+      </c>
+      <c r="M64" t="s">
+        <v>157</v>
+      </c>
+      <c r="N64" t="s">
+        <v>158</v>
+      </c>
+      <c r="O64" t="s">
+        <v>205</v>
+      </c>
+      <c r="P64" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>1</v>
+      </c>
+      <c r="B65" t="s">
+        <v>207</v>
+      </c>
+      <c r="C65" t="s">
+        <v>208</v>
+      </c>
+      <c r="E65" t="s">
+        <v>154</v>
+      </c>
+      <c r="F65" t="s">
+        <v>44</v>
+      </c>
+      <c r="I65" t="s">
+        <v>209</v>
+      </c>
+      <c r="J65" t="s">
+        <v>207</v>
+      </c>
+      <c r="L65" t="s">
+        <v>210</v>
+      </c>
+      <c r="M65" t="s">
+        <v>211</v>
+      </c>
+      <c r="N65" t="s">
+        <v>212</v>
+      </c>
+      <c r="O65" t="s">
+        <v>208</v>
+      </c>
+      <c r="P65" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>1</v>
+      </c>
+      <c r="B66" t="s">
+        <v>207</v>
+      </c>
+      <c r="C66" t="s">
+        <v>213</v>
+      </c>
+      <c r="E66" t="s">
+        <v>154</v>
+      </c>
+      <c r="F66" t="s">
+        <v>44</v>
+      </c>
+      <c r="I66" t="s">
+        <v>214</v>
+      </c>
+      <c r="J66" t="s">
+        <v>207</v>
+      </c>
+      <c r="L66" t="s">
+        <v>210</v>
+      </c>
+      <c r="M66" t="s">
+        <v>211</v>
+      </c>
+      <c r="N66" t="s">
+        <v>212</v>
+      </c>
+      <c r="O66" t="s">
+        <v>213</v>
+      </c>
+      <c r="P66" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>1</v>
+      </c>
+      <c r="B67" t="s">
+        <v>207</v>
+      </c>
+      <c r="C67" t="s">
+        <v>215</v>
+      </c>
+      <c r="E67" t="s">
+        <v>154</v>
+      </c>
+      <c r="F67" t="s">
+        <v>44</v>
+      </c>
+      <c r="I67" t="s">
+        <v>216</v>
+      </c>
+      <c r="J67" t="s">
+        <v>207</v>
+      </c>
+      <c r="L67" t="s">
+        <v>210</v>
+      </c>
+      <c r="M67" t="s">
+        <v>211</v>
+      </c>
+      <c r="N67" t="s">
+        <v>212</v>
+      </c>
+      <c r="O67" t="s">
+        <v>215</v>
+      </c>
+      <c r="P67" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>1</v>
+      </c>
+      <c r="B68" t="s">
+        <v>207</v>
+      </c>
+      <c r="C68" t="s">
+        <v>217</v>
+      </c>
+      <c r="E68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F68" t="s">
+        <v>44</v>
+      </c>
+      <c r="I68" t="s">
+        <v>218</v>
+      </c>
+      <c r="J68" t="s">
+        <v>207</v>
+      </c>
+      <c r="L68" t="s">
+        <v>210</v>
+      </c>
+      <c r="M68" t="s">
+        <v>211</v>
+      </c>
+      <c r="N68" t="s">
+        <v>212</v>
+      </c>
+      <c r="O68" t="s">
+        <v>217</v>
+      </c>
+      <c r="P68" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B69" t="s">
+        <v>207</v>
+      </c>
+      <c r="C69" t="s">
+        <v>219</v>
+      </c>
+      <c r="E69" t="s">
+        <v>154</v>
+      </c>
+      <c r="F69" t="s">
+        <v>44</v>
+      </c>
+      <c r="I69" t="s">
+        <v>220</v>
+      </c>
+      <c r="J69" t="s">
+        <v>207</v>
+      </c>
+      <c r="L69" t="s">
+        <v>210</v>
+      </c>
+      <c r="M69" t="s">
+        <v>211</v>
+      </c>
+      <c r="N69" t="s">
+        <v>212</v>
+      </c>
+      <c r="O69" t="s">
+        <v>219</v>
+      </c>
+      <c r="P69" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>1</v>
+      </c>
+      <c r="B70" t="s">
+        <v>207</v>
+      </c>
+      <c r="C70" t="s">
+        <v>221</v>
+      </c>
+      <c r="E70" t="s">
+        <v>154</v>
+      </c>
+      <c r="F70" t="s">
+        <v>44</v>
+      </c>
+      <c r="I70" t="s">
+        <v>222</v>
+      </c>
+      <c r="J70" t="s">
+        <v>207</v>
+      </c>
+      <c r="L70" t="s">
+        <v>210</v>
+      </c>
+      <c r="M70" t="s">
+        <v>211</v>
+      </c>
+      <c r="N70" t="s">
+        <v>212</v>
+      </c>
+      <c r="O70" t="s">
+        <v>221</v>
+      </c>
+      <c r="P70" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B71" t="s">
+        <v>207</v>
+      </c>
+      <c r="C71" t="s">
+        <v>223</v>
+      </c>
+      <c r="E71" t="s">
+        <v>154</v>
+      </c>
+      <c r="F71" t="s">
+        <v>44</v>
+      </c>
+      <c r="I71" t="s">
+        <v>224</v>
+      </c>
+      <c r="J71" t="s">
+        <v>207</v>
+      </c>
+      <c r="L71" t="s">
+        <v>210</v>
+      </c>
+      <c r="M71" t="s">
+        <v>211</v>
+      </c>
+      <c r="N71" t="s">
+        <v>212</v>
+      </c>
+      <c r="O71" t="s">
+        <v>223</v>
+      </c>
+      <c r="P71" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>1</v>
+      </c>
+      <c r="B72" t="s">
+        <v>207</v>
+      </c>
+      <c r="C72" t="s">
+        <v>225</v>
+      </c>
+      <c r="E72" t="s">
+        <v>154</v>
+      </c>
+      <c r="F72" t="s">
+        <v>44</v>
+      </c>
+      <c r="I72" t="s">
+        <v>226</v>
+      </c>
+      <c r="J72" t="s">
+        <v>207</v>
+      </c>
+      <c r="L72" t="s">
+        <v>210</v>
+      </c>
+      <c r="M72" t="s">
+        <v>211</v>
+      </c>
+      <c r="N72" t="s">
+        <v>212</v>
+      </c>
+      <c r="O72" t="s">
+        <v>225</v>
+      </c>
+      <c r="P72" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>1</v>
+      </c>
+      <c r="B73" t="s">
+        <v>207</v>
+      </c>
+      <c r="C73" t="s">
+        <v>227</v>
+      </c>
+      <c r="E73" t="s">
+        <v>154</v>
+      </c>
+      <c r="F73" t="s">
+        <v>44</v>
+      </c>
+      <c r="I73" t="s">
+        <v>228</v>
+      </c>
+      <c r="J73" t="s">
+        <v>207</v>
+      </c>
+      <c r="L73" t="s">
+        <v>210</v>
+      </c>
+      <c r="M73" t="s">
+        <v>211</v>
+      </c>
+      <c r="N73" t="s">
+        <v>212</v>
+      </c>
+      <c r="O73" t="s">
+        <v>227</v>
+      </c>
+      <c r="P73" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>1</v>
+      </c>
+      <c r="B74" t="s">
+        <v>207</v>
+      </c>
+      <c r="C74" t="s">
+        <v>229</v>
+      </c>
+      <c r="E74" t="s">
+        <v>154</v>
+      </c>
+      <c r="F74" t="s">
+        <v>44</v>
+      </c>
+      <c r="I74" t="s">
+        <v>230</v>
+      </c>
+      <c r="J74" t="s">
+        <v>207</v>
+      </c>
+      <c r="L74" t="s">
+        <v>210</v>
+      </c>
+      <c r="M74" t="s">
+        <v>211</v>
+      </c>
+      <c r="N74" t="s">
+        <v>212</v>
+      </c>
+      <c r="O74" t="s">
+        <v>229</v>
+      </c>
+      <c r="P74" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>1</v>
+      </c>
+      <c r="B75" t="s">
+        <v>231</v>
+      </c>
+      <c r="E75" t="s">
+        <v>43</v>
+      </c>
+      <c r="F75" t="s">
+        <v>44</v>
+      </c>
+      <c r="J75" t="s">
+        <v>231</v>
+      </c>
+      <c r="L75" t="s">
+        <v>235</v>
+      </c>
+      <c r="M75" t="s">
+        <v>239</v>
+      </c>
+      <c r="N75" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>1</v>
+      </c>
+      <c r="B76" t="s">
+        <v>232</v>
+      </c>
+      <c r="E76" t="s">
+        <v>43</v>
+      </c>
+      <c r="F76" t="s">
+        <v>44</v>
+      </c>
+      <c r="J76" t="s">
+        <v>232</v>
+      </c>
+      <c r="L76" t="s">
+        <v>238</v>
+      </c>
+      <c r="M76" t="s">
+        <v>240</v>
+      </c>
+      <c r="N76" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>1</v>
+      </c>
+      <c r="B77" t="s">
+        <v>233</v>
+      </c>
+      <c r="E77" t="s">
+        <v>43</v>
+      </c>
+      <c r="F77" t="s">
+        <v>44</v>
+      </c>
+      <c r="J77" t="s">
+        <v>233</v>
+      </c>
+      <c r="L77" t="s">
+        <v>236</v>
+      </c>
+      <c r="M77" t="s">
+        <v>241</v>
+      </c>
+      <c r="N77" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>1</v>
+      </c>
+      <c r="B78" t="s">
         <v>234</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E78" t="s">
         <v>43</v>
       </c>
-      <c r="F64" t="s">
-        <v>44</v>
-      </c>
-      <c r="J64" t="s">
+      <c r="F78" t="s">
+        <v>44</v>
+      </c>
+      <c r="J78" t="s">
         <v>234</v>
       </c>
-      <c r="L64" t="s">
+      <c r="L78" t="s">
         <v>237</v>
       </c>
-      <c r="M64" t="s">
+      <c r="M78" t="s">
         <v>242</v>
       </c>
-      <c r="N64" t="s">
+      <c r="N78" t="s">
         <v>246</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C22:C26 C28">
+  <conditionalFormatting sqref="C36:C40 C42">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I25">
+  <conditionalFormatting sqref="I36:I39">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I26 I28">
+  <conditionalFormatting sqref="I40 I42">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/variable_schema_data_individual_roster_template.xlsx
+++ b/resources/variable_schema_data_individual_roster_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB383FE-3EB9-4BD4-86D8-E15F5243DD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1EF71B-9D9F-444E-808A-F8377E8A0D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14280" yWindow="0" windowWidth="14625" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
